--- a/data/legislation/screening/screening_matches.xlsx
+++ b/data/legislation/screening/screening_matches.xlsx
@@ -553,7 +553,7 @@
     <t>Decreto de Aprobación del "Acuerdo Regional sobre el Acceso a la Información, la Participación Pública y el Acceso a la Justicia en Asuntos Ambientales en América Latina y el Caribe"</t>
   </si>
   <si>
-    <t>DECRETO DE APROBACIÓN DEL PROTOCOLO NAGOYA SOBRE ACCESO A LOS RECURSOS GENÉTICO Y PARTICIPACIÓN JUSTA Y EQUITATIVA EN LOS BENEFICIOS QUE SE DERIVEN DE SU UTILIZACIÓN AL CONVENIO SOBRE DIVERSIDAD BIOLÓGICA</t>
+    <t>Decreto de Aprobación del Protocolo Nagoya sobre Acceso a los Recursos Genético y Participación Justa y Equitativa en los Beneficios que se Deriven de su Utilización al Convenio sobre Diversidad Biológica</t>
   </si>
   <si>
     <t>Ley de Reforma a la Ley N°. 620, Ley General de Aguas Nacionales</t>
